--- a/artfynd/A 57179-2025 artfynd.xlsx
+++ b/artfynd/A 57179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121378487</v>
+        <v>121376762</v>
       </c>
       <c r="B2" t="n">
-        <v>97279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690499</v>
+        <v>690230</v>
       </c>
       <c r="R2" t="n">
-        <v>7129884</v>
+        <v>7129968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,57 +760,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129001305</v>
+        <v>121376668</v>
       </c>
       <c r="B3" t="n">
-        <v>91573</v>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyliden, Ly lm</t>
+          <t>Frögliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690438</v>
+        <v>690214</v>
       </c>
       <c r="R3" t="n">
-        <v>7129865</v>
+        <v>7129957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,15 +861,116 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121378487</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Frögliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>690499</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7129884</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57179-2025 artfynd.xlsx
+++ b/artfynd/A 57179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376762</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376668</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,8 +986,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121378487</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>